--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5AB597-F950-4988-BB75-E14C7207E27A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6B1434-7F8C-472E-B305-F48251AC7B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="2100" windowWidth="25680" windowHeight="19110" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="76695" yWindow="5025" windowWidth="25950" windowHeight="13170" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>год</t>
   </si>
@@ -125,6 +125,15 @@
   </si>
   <si>
     <t>Варшавская</t>
+  </si>
+  <si>
+    <t>чж</t>
+  </si>
+  <si>
+    <t>Самаркандская обл.</t>
+  </si>
+  <si>
+    <t>экстраполяция из участка 1888-1900</t>
   </si>
 </sst>
 </file>
@@ -172,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -183,11 +192,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -209,9 +214,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -249,7 +254,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -355,7 +360,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,7 +502,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -506,9 +511,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E727C47-D865-4836-8CF2-7B9647F06C78}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -520,16 +525,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:T55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U61"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.89453125" customWidth="1"/>
+    <col min="3" max="3" width="11.68359375" customWidth="1"/>
+    <col min="4" max="5" width="18.26171875" customWidth="1"/>
+    <col min="6" max="6" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
@@ -543,27 +548,31 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>1897</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="4"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="7">
         <v>1911</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -572,12 +581,13 @@
       <c r="D3" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>1906</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -586,12 +596,13 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>1909</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -600,35 +611,37 @@
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>1898</v>
       </c>
       <c r="C6" s="2">
         <v>52166</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>1899</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <v>1906</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -637,23 +650,25 @@
       <c r="D8" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>1898</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>1911</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -662,26 +677,27 @@
       <c r="D10" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>1901</v>
       </c>
       <c r="C11" s="2">
         <v>103114</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="7">
         <v>1904</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -690,12 +706,13 @@
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>1907</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -704,12 +721,13 @@
       <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="7">
         <v>1913</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -718,309 +736,416 @@
       <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>1902</v>
       </c>
       <c r="C15" s="2">
         <v>3820</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="7">
         <v>1902</v>
       </c>
       <c r="C16" s="2">
         <v>14958</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="7">
+        <v>1881</v>
+      </c>
+      <c r="E17" s="2">
+        <v>575000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1882</v>
+      </c>
+      <c r="E18" s="2">
+        <v>589000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="7">
+        <v>1883</v>
+      </c>
+      <c r="E19" s="2">
+        <v>603000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1884</v>
+      </c>
+      <c r="E20" s="2">
+        <v>618000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="7">
+        <v>1885</v>
+      </c>
+      <c r="E21" s="2">
+        <v>633000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E22" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E23" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="3"/>
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
       <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M34" s="2"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="K36" s="2"/>
+      <c r="J36" s="2"/>
       <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M36" s="2"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O37" s="3"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="N44" s="2"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="N45" s="2"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="N46" s="2"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-      <c r="N47" s="2"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="N48" s="2"/>
-    </row>
-    <row r="49" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N49" s="2"/>
-    </row>
-    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N50" s="2"/>
-    </row>
-    <row r="51" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N51" s="2"/>
-    </row>
-    <row r="52" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N52" s="2"/>
-    </row>
-    <row r="53" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N53" s="2"/>
-    </row>
-    <row r="54" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N54" s="2"/>
-    </row>
-    <row r="55" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N55" s="2"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="O50" s="2"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="O51" s="2"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="O52" s="2"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O61" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6B1434-7F8C-472E-B305-F48251AC7B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6281638-20AF-4F73-AE87-F4285FD6ADDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76695" yWindow="5025" windowWidth="25950" windowHeight="13170" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
   <si>
     <t>год</t>
   </si>
@@ -74,12 +74,6 @@
   </si>
   <si>
     <t>Якутская обл.</t>
-  </si>
-  <si>
-    <t>г. Николаев</t>
-  </si>
-  <si>
-    <t>г. Одесса</t>
   </si>
   <si>
     <t>примечание</t>
@@ -515,7 +509,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.89453125" customWidth="1"/>
@@ -548,22 +542,22 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" s="7">
         <v>1897</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
@@ -576,10 +570,10 @@
         <v>1911</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -591,10 +585,10 @@
         <v>1906</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -606,10 +600,10 @@
         <v>1909</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -633,7 +627,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4"/>
     </row>
@@ -645,10 +639,10 @@
         <v>1906</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -660,7 +654,7 @@
         <v>1898</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -672,10 +666,10 @@
         <v>1911</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4"/>
     </row>
@@ -690,7 +684,7 @@
         <v>103114</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -701,10 +695,10 @@
         <v>1904</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -716,10 +710,10 @@
         <v>1907</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -731,175 +725,177 @@
         <v>1913</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B15" s="7">
-        <v>1902</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3820</v>
+        <v>1881</v>
+      </c>
+      <c r="E15" s="2">
+        <v>575000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1882</v>
+      </c>
+      <c r="E16" s="2">
+        <v>589000</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="7">
+        <v>1883</v>
+      </c>
+      <c r="E17" s="2">
+        <v>603000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1884</v>
+      </c>
+      <c r="E18" s="2">
+        <v>618000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="7">
+        <v>1885</v>
+      </c>
+      <c r="E19" s="2">
+        <v>633000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E20" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E21" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="7">
-        <v>1902</v>
-      </c>
-      <c r="C16" s="2">
-        <v>14958</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E17" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E18" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E19" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="7">
-        <v>1884</v>
-      </c>
-      <c r="E20" s="2">
-        <v>618000</v>
-      </c>
-      <c r="F20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="7">
-        <v>1885</v>
-      </c>
-      <c r="E21" s="2">
-        <v>633000</v>
-      </c>
-      <c r="F21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="7">
-        <v>1886</v>
-      </c>
-      <c r="E22" s="2">
-        <v>648000</v>
-      </c>
-      <c r="F22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="7">
-        <v>1887</v>
-      </c>
-      <c r="E23" s="2">
-        <v>664000</v>
-      </c>
-      <c r="F23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1" t="s">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>26</v>
-      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
       <c r="O33" s="3"/>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="G34" s="2"/>
@@ -911,41 +907,41 @@
       <c r="O34" s="3"/>
       <c r="P34" s="2"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
       <c r="O35" s="3"/>
       <c r="P35" s="2"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="O36" s="3"/>
       <c r="P36" s="2"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="2"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="G38" s="2"/>
@@ -955,13 +951,8 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="G39" s="2"/>
@@ -969,46 +960,47 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="G44" s="2"/>
@@ -1018,27 +1010,27 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="G47" s="2"/>
@@ -1048,15 +1040,14 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="O48" s="2"/>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="2"/>
@@ -1067,20 +1058,25 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
+      <c r="O49" s="2"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="G50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
       <c r="O50" s="2"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -1089,32 +1085,14 @@
       <c r="O51" s="2"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
       <c r="O52" s="2"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
       <c r="O53" s="2"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
       <c r="O54" s="2"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1131,12 +1109,6 @@
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O59" s="2"/>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O60" s="2"/>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O61" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6281638-20AF-4F73-AE87-F4285FD6ADDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5B5AAA-BAA6-45AB-9E48-A15C30C29CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="80280" yWindow="4110" windowWidth="22185" windowHeight="13620" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
   <si>
     <t>год</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>экстраполяция из участка 1888-1900</t>
+  </si>
+  <si>
+    <t>Бессарабская</t>
   </si>
 </sst>
 </file>
@@ -519,7 +522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U59"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.89453125" customWidth="1"/>
@@ -830,56 +833,61 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1" t="s">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C22" s="2">
+        <v>100432</v>
+      </c>
+      <c r="D22" s="2">
+        <v>76687</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2472605</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
       <c r="O32" s="3"/>
       <c r="P32" s="2"/>
     </row>
@@ -914,6 +922,8 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
       <c r="O35" s="3"/>
       <c r="P35" s="2"/>
     </row>
@@ -924,14 +934,8 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
       <c r="O36" s="3"/>
       <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="2"/>
@@ -940,6 +944,14 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="2"/>
@@ -948,9 +960,6 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="2"/>
@@ -959,6 +968,9 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="2"/>
@@ -967,8 +979,6 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
     </row>
     <row r="41" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="2"/>
@@ -977,8 +987,8 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
       <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2"/>
@@ -997,8 +1007,8 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="2"/>
@@ -1007,8 +1017,8 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="2"/>
@@ -1027,8 +1037,8 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2"/>
@@ -1037,8 +1047,8 @@
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
     </row>
     <row r="48" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="2"/>
@@ -1047,7 +1057,8 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="2"/>
@@ -1056,15 +1067,12 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
       <c r="O49" s="2"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -1085,11 +1093,20 @@
       <c r="O51" s="2"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
       <c r="O52" s="2"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
       <c r="O53" s="2"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1109,6 +1126,9 @@
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O59" s="2"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O60" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5B5AAA-BAA6-45AB-9E48-A15C30C29CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63789324-43D1-4AB1-AA79-03F2EDB6BC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80280" yWindow="4110" windowWidth="22185" windowHeight="13620" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="61275" yWindow="1110" windowWidth="30735" windowHeight="18270" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
   <si>
     <t>год</t>
   </si>
@@ -522,7 +522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U60"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.89453125" customWidth="1"/>
@@ -626,91 +626,90 @@
         <v>8</v>
       </c>
       <c r="B7" s="7">
-        <v>1899</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C7" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D7" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>1899</v>
+      </c>
+      <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="7">
-        <v>1898</v>
+        <v>1906</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
+        <v>1898</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C11" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
+        <v>1911</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="4"/>
+        <v>1901</v>
+      </c>
+      <c r="C12" s="2">
+        <v>103114</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>20</v>
@@ -725,7 +724,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>20</v>
@@ -737,173 +736,176 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E15" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E16" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E17" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E18" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E19" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E20" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E21" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E22" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B23" s="7">
         <v>1914</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C23" s="2">
         <v>100432</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D23" s="2">
         <v>76687</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E23" s="2">
         <v>2472605</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="2"/>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
       <c r="O33" s="3"/>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="G34" s="2"/>
@@ -915,7 +917,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="2"/>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="G35" s="2"/>
@@ -927,80 +929,82 @@
       <c r="O35" s="3"/>
       <c r="P35" s="2"/>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
       <c r="O36" s="3"/>
       <c r="P36" s="2"/>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
       <c r="O37" s="3"/>
       <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
-    </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
       <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="G43" s="2"/>
@@ -1010,27 +1014,27 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="G46" s="2"/>
@@ -1040,25 +1044,25 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="2"/>
@@ -1067,7 +1071,8 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="2"/>
@@ -1076,15 +1081,12 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
       <c r="O50" s="2"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
+      <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -1105,11 +1107,20 @@
       <c r="O52" s="2"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
       <c r="O53" s="2"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
       <c r="O54" s="2"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1129,6 +1140,9 @@
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O60" s="2"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O61" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63789324-43D1-4AB1-AA79-03F2EDB6BC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFC543D-C893-41EA-97C7-03BB18960914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61275" yWindow="1110" windowWidth="30735" windowHeight="18270" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="82950" yWindow="2415" windowWidth="23235" windowHeight="12435" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
   <si>
     <t>год</t>
   </si>
@@ -131,6 +131,18 @@
   </si>
   <si>
     <t>Бессарабская</t>
+  </si>
+  <si>
+    <t>Калишская</t>
+  </si>
+  <si>
+    <t>Келецкая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сувалкская </t>
+  </si>
+  <si>
+    <t>Седлецкая</t>
   </si>
 </sst>
 </file>
@@ -178,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -192,6 +204,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.89453125" customWidth="1"/>
@@ -597,394 +612,404 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B5" s="7">
-        <v>1909</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>20</v>
+        <v>1886</v>
+      </c>
+      <c r="C5" s="8">
+        <v>31028</v>
+      </c>
+      <c r="D5" s="8">
+        <v>19278</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B6" s="7">
-        <v>1898</v>
-      </c>
-      <c r="C6" s="2">
-        <v>52166</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8">
+        <v>16904</v>
+      </c>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C7" s="2">
-        <v>47652</v>
-      </c>
-      <c r="D7" s="2">
-        <v>28698</v>
-      </c>
+        <v>1909</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7">
-        <v>1899</v>
+        <v>1882</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
-        <v>23</v>
+      <c r="D8" s="8">
+        <v>23374</v>
       </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>26</v>
+        <v>1889</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="8">
+        <v>29004</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" s="7">
         <v>1898</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="4"/>
+      <c r="C10" s="2">
+        <v>52166</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B11" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C11" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D11" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B12" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C12" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
+        <v>1899</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B13" s="7">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" s="7">
-        <v>1907</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>20</v>
+        <v>1898</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B15" s="7">
-        <v>1913</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B16" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E16" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
+        <v>1892</v>
+      </c>
+      <c r="D16" s="8">
+        <v>19117</v>
+      </c>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B17" s="7">
         <v>1882</v>
       </c>
-      <c r="E17" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>31</v>
-      </c>
+      <c r="D17" s="8">
+        <v>15122</v>
+      </c>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B18" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E18" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F18" t="s">
-        <v>31</v>
-      </c>
+        <v>1911</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B19" s="7">
-        <v>1884</v>
-      </c>
-      <c r="E19" s="2">
-        <v>618000</v>
+        <v>1901</v>
+      </c>
+      <c r="C19" s="2">
+        <v>103114</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B20" s="7">
-        <v>1885</v>
-      </c>
-      <c r="E20" s="2">
-        <v>633000</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B21" s="7">
-        <v>1886</v>
-      </c>
-      <c r="E21" s="2">
-        <v>648000</v>
-      </c>
-      <c r="F21" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7">
-        <v>1887</v>
-      </c>
-      <c r="E22" s="2">
-        <v>664000</v>
-      </c>
-      <c r="F22" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C23" s="2">
-        <v>100432</v>
-      </c>
-      <c r="D23" s="2">
-        <v>76687</v>
+        <v>1881</v>
       </c>
       <c r="E23" s="2">
-        <v>2472605</v>
+        <v>575000</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="7">
+        <v>1882</v>
+      </c>
+      <c r="E24" s="2">
+        <v>589000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1" t="s">
-        <v>15</v>
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="7">
+        <v>1883</v>
+      </c>
+      <c r="E25" s="2">
+        <v>603000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="7">
+        <v>1884</v>
+      </c>
+      <c r="E26" s="2">
+        <v>618000</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="B27" s="7">
+        <v>1885</v>
+      </c>
+      <c r="E27" s="2">
+        <v>633000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="B28" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E28" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E29" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C30" s="2">
+        <v>100432</v>
+      </c>
+      <c r="D30" s="2">
+        <v>76687</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2472605</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="2"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="2"/>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="2"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="2"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="2"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="2"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="2"/>
@@ -993,6 +1018,10 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="2"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2"/>
@@ -1003,6 +1032,8 @@
       <c r="J42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="2"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="2"/>
@@ -1011,8 +1042,10 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
       <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="2"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="2"/>
@@ -1021,8 +1054,8 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="2"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="2"/>
@@ -1031,8 +1064,14 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="2"/>
@@ -1041,8 +1080,6 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2"/>
@@ -1053,6 +1090,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="2"/>
@@ -1061,8 +1099,6 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="2"/>
@@ -1071,8 +1107,8 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
       <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="2"/>
@@ -1081,7 +1117,8 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="2"/>
@@ -1092,57 +1129,126 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
-      <c r="O51" s="2"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+      <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
+      <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-      <c r="O53" s="2"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="O54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
       <c r="O57" s="2"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
       <c r="O58" s="2"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
       <c r="O59" s="2"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
       <c r="O60" s="2"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
       <c r="O61" s="2"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O66" s="2"/>
+    </row>
+    <row r="67" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O67" s="2"/>
+    </row>
+    <row r="68" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O68" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFC543D-C893-41EA-97C7-03BB18960914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35B0D24-9F19-41AF-817E-BD5F1C53A6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="82950" yWindow="2415" windowWidth="23235" windowHeight="12435" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
   <si>
     <t>год</t>
   </si>
@@ -143,6 +143,12 @@
   </si>
   <si>
     <t>Седлецкая</t>
+  </si>
+  <si>
+    <t>Радомская</t>
+  </si>
+  <si>
+    <t>г. Варшава</t>
   </si>
 </sst>
 </file>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -206,6 +212,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -537,7 +549,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U68"/>
+  <dimension ref="A1:U74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.89453125" customWidth="1"/>
@@ -570,80 +582,82 @@
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="7">
-        <v>1897</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="4"/>
+      <c r="B2" s="9">
+        <v>1882</v>
+      </c>
+      <c r="C2" s="10">
+        <v>37996</v>
+      </c>
+      <c r="D2" s="10">
+        <v>26885</v>
+      </c>
+      <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="B3" s="9">
+        <v>1885</v>
+      </c>
+      <c r="C3" s="10">
+        <v>40820</v>
+      </c>
+      <c r="D3" s="10">
+        <v>25230</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1893</v>
+      </c>
+      <c r="C4" s="10">
+        <v>47775</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C5" s="8">
-        <v>31028</v>
-      </c>
-      <c r="D5" s="8">
-        <v>19278</v>
+        <v>1897</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B6" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8">
-        <v>16904</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C6" s="10">
+        <v>14299</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>20</v>
@@ -655,299 +669,299 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="8">
-        <v>23374</v>
+        <v>1906</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B9" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>1886</v>
+      </c>
+      <c r="C9" s="8">
+        <v>31028</v>
+      </c>
       <c r="D9" s="8">
-        <v>29004</v>
+        <v>19278</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B10" s="7">
-        <v>1898</v>
-      </c>
-      <c r="C10" s="2">
-        <v>52166</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8">
+        <v>16904</v>
+      </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C11" s="2">
-        <v>47652</v>
-      </c>
-      <c r="D11" s="2">
-        <v>28698</v>
-      </c>
+        <v>1909</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="7">
-        <v>1899</v>
+        <v>1882</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4" t="s">
-        <v>23</v>
+      <c r="D12" s="8">
+        <v>23374</v>
       </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>26</v>
+        <v>1889</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="8">
+        <v>29004</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14" s="7">
         <v>1898</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="4"/>
+      <c r="C14" s="2">
+        <v>52166</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B15" s="7">
-        <v>1882</v>
+        <v>1889</v>
       </c>
       <c r="C15" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+        <v>47652</v>
+      </c>
+      <c r="D15" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B16" s="7">
-        <v>1892</v>
-      </c>
-      <c r="D16" s="8">
-        <v>19117</v>
+        <v>1899</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B17" s="7">
-        <v>1882</v>
-      </c>
-      <c r="D17" s="8">
-        <v>15122</v>
+        <v>1906</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B18" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>20</v>
+        <v>1889</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="8">
+        <v>18552</v>
       </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B19" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C19" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
+        <v>1898</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B20" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C20" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B21" s="7">
-        <v>1907</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>20</v>
+        <v>1886</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="8">
+        <v>16816</v>
       </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B22" s="7">
-        <v>1913</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>20</v>
+        <v>1892</v>
+      </c>
+      <c r="D22" s="8">
+        <v>19117</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B23" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E23" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F23" t="s">
-        <v>31</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="D23" s="8">
+        <v>15122</v>
+      </c>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B24" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E24" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F24" t="s">
-        <v>31</v>
-      </c>
+        <v>1911</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B25" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E25" s="2">
-        <v>603000</v>
+        <v>1901</v>
+      </c>
+      <c r="C25" s="2">
+        <v>103114</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B26" s="7">
-        <v>1884</v>
-      </c>
-      <c r="E26" s="2">
-        <v>618000</v>
-      </c>
-      <c r="F26" t="s">
-        <v>31</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B27" s="7">
-        <v>1885</v>
-      </c>
-      <c r="E27" s="2">
-        <v>633000</v>
-      </c>
-      <c r="F27" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B28" s="7">
-        <v>1886</v>
-      </c>
-      <c r="E28" s="2">
-        <v>648000</v>
-      </c>
-      <c r="F28" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="7">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="E29" s="2">
-        <v>664000</v>
+        <v>575000</v>
       </c>
       <c r="F29" t="s">
         <v>31</v>
@@ -955,152 +969,171 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="7">
+        <v>1882</v>
+      </c>
+      <c r="E30" s="2">
+        <v>589000</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7">
+        <v>1883</v>
+      </c>
+      <c r="E31" s="2">
+        <v>603000</v>
+      </c>
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7">
+        <v>1884</v>
+      </c>
+      <c r="E32" s="2">
+        <v>618000</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="7">
+        <v>1885</v>
+      </c>
+      <c r="E33" s="2">
+        <v>633000</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E34" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E35" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B36" s="7">
         <v>1914</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C36" s="2">
         <v>100432</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D36" s="2">
         <v>76687</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E36" s="2">
         <v>2472605</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="1" t="s">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="2"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="2"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="2"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="2"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="2"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="O46" s="3"/>
+      <c r="P46" s="2"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="O47" s="3"/>
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="2"/>
+    </row>
+    <row r="49" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="G49" s="2"/>
@@ -1109,18 +1142,20 @@
       <c r="J49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O49" s="3"/>
+      <c r="P49" s="2"/>
+    </row>
+    <row r="50" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O50" s="3"/>
+      <c r="P50" s="2"/>
+    </row>
+    <row r="51" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="G51" s="2"/>
@@ -1129,18 +1164,22 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M51" s="2"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2"/>
+    </row>
+    <row r="52" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="53" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="G53" s="2"/>
@@ -1149,28 +1188,27 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="55" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="G56" s="2"/>
@@ -1180,75 +1218,135 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
-      <c r="O57" s="2"/>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="O58" s="2"/>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
+      <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-      <c r="O59" s="2"/>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="60" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+      <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
-      <c r="O60" s="2"/>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="61" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
-      <c r="O61" s="2"/>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O62" s="2"/>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="62" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
       <c r="O64" s="2"/>
     </row>
-    <row r="65" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O68" s="2"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O69" s="2"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O70" s="2"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O71" s="2"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O72" s="2"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O73" s="2"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O74" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35B0D24-9F19-41AF-817E-BD5F1C53A6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56BAC84-8BE3-492D-AD72-B44ABA9BFED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="81840" yWindow="3660" windowWidth="23235" windowHeight="12240" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="39">
   <si>
     <t>год</t>
   </si>
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -212,12 +212,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -549,7 +543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U74"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.89453125" customWidth="1"/>
@@ -582,13 +576,13 @@
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="7">
         <v>1882</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="8">
         <v>37996</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="8">
         <v>26885</v>
       </c>
       <c r="E2" s="5"/>
@@ -598,13 +592,13 @@
       <c r="A3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="7">
         <v>1885</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="8">
         <v>40820</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="8">
         <v>25230</v>
       </c>
       <c r="E3" s="5"/>
@@ -614,13 +608,13 @@
       <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>1893</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>47775</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
@@ -645,7 +639,7 @@
       <c r="B6" s="7">
         <v>1882</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="8">
         <v>14299</v>
       </c>
       <c r="D6" s="4"/>
@@ -654,25 +648,26 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B7" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>20</v>
+        <v>1885</v>
+      </c>
+      <c r="C7" s="8">
+        <v>14570</v>
+      </c>
+      <c r="D7" s="8">
+        <v>11807</v>
       </c>
       <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="7">
-        <v>1906</v>
+        <v>1911</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>20</v>
@@ -684,57 +679,59 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B9" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C9" s="8">
-        <v>31028</v>
-      </c>
-      <c r="D9" s="8">
-        <v>19278</v>
+        <v>1906</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C10" s="8"/>
+        <v>1886</v>
+      </c>
+      <c r="C10" s="8">
+        <v>31028</v>
+      </c>
       <c r="D10" s="8">
-        <v>16904</v>
+        <v>19278</v>
       </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B11" s="7">
-        <v>1909</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>20</v>
+        <v>1889</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8">
+        <v>16904</v>
       </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="8">
-        <v>23374</v>
+        <v>1909</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -743,11 +740,11 @@
         <v>7</v>
       </c>
       <c r="B13" s="7">
-        <v>1889</v>
+        <v>1882</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="8">
-        <v>29004</v>
+        <v>23374</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -756,24 +753,23 @@
         <v>7</v>
       </c>
       <c r="B14" s="7">
-        <v>1898</v>
-      </c>
-      <c r="C14" s="2">
-        <v>52166</v>
-      </c>
+        <v>1889</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="8">
+        <v>29004</v>
+      </c>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="7">
-        <v>1889</v>
+        <v>1898</v>
       </c>
       <c r="C15" s="2">
-        <v>47652</v>
-      </c>
-      <c r="D15" s="2">
-        <v>28698</v>
+        <v>52166</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -781,65 +777,66 @@
         <v>8</v>
       </c>
       <c r="B16" s="7">
-        <v>1899</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C16" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D16" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>1899</v>
+      </c>
+      <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B18" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="8">
-        <v>18552</v>
+        <v>1906</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B19" s="7">
-        <v>1898</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>27</v>
+        <v>1889</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="8">
+        <v>18552</v>
       </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B20" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C20" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D20" s="4"/>
+        <v>1898</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -847,12 +844,12 @@
         <v>36</v>
       </c>
       <c r="B21" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="8">
-        <v>16816</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C21" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -860,75 +857,73 @@
         <v>36</v>
       </c>
       <c r="B22" s="7">
-        <v>1892</v>
-      </c>
+        <v>1886</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" s="8">
-        <v>19117</v>
+        <v>16816</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" s="7">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="D23" s="8">
-        <v>15122</v>
+        <v>19117</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>20</v>
+        <v>1882</v>
+      </c>
+      <c r="D24" s="8">
+        <v>15122</v>
       </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C25" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F25" t="s">
-        <v>25</v>
-      </c>
+        <v>1911</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="4"/>
+        <v>1901</v>
+      </c>
+      <c r="C26" s="2">
+        <v>103114</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>20</v>
@@ -943,7 +938,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="7">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>20</v>
@@ -955,27 +950,28 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B29" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E29" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F29" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E30" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F30" t="s">
         <v>31</v>
@@ -986,10 +982,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E31" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -1000,10 +996,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E32" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F32" t="s">
         <v>31</v>
@@ -1014,10 +1010,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E33" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -1028,10 +1024,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E34" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F34" t="s">
         <v>31</v>
@@ -1042,10 +1038,10 @@
         <v>30</v>
       </c>
       <c r="B35" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E35" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F35" t="s">
         <v>31</v>
@@ -1053,71 +1049,73 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E36" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B37" s="7">
         <v>1914</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C37" s="2">
         <v>100432</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D37" s="2">
         <v>76687</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E37" s="2">
         <v>2472605</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="2"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
       <c r="O47" s="3"/>
       <c r="P47" s="2"/>
     </row>
@@ -1152,6 +1150,8 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
       <c r="O50" s="3"/>
       <c r="P50" s="2"/>
     </row>
@@ -1162,14 +1162,8 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
       <c r="O51" s="3"/>
       <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
     </row>
     <row r="52" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="2"/>
@@ -1178,6 +1172,14 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
     </row>
     <row r="53" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="2"/>
@@ -1186,9 +1188,6 @@
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
     </row>
     <row r="54" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="2"/>
@@ -1197,6 +1196,9 @@
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
     </row>
     <row r="55" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="2"/>
@@ -1205,8 +1207,6 @@
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
     </row>
     <row r="56" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="2"/>
@@ -1215,8 +1215,8 @@
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
       <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
     </row>
     <row r="57" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="2"/>
@@ -1235,8 +1235,8 @@
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="2"/>
@@ -1245,8 +1245,8 @@
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
     </row>
     <row r="60" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="2"/>
@@ -1265,8 +1265,8 @@
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="2"/>
@@ -1275,8 +1275,8 @@
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="2"/>
@@ -1285,7 +1285,8 @@
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="2"/>
@@ -1294,15 +1295,12 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
       <c r="O64" s="2"/>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -1323,11 +1321,20 @@
       <c r="O66" s="2"/>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
       <c r="O67" s="2"/>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
       <c r="O68" s="2"/>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.55000000000000004">
@@ -1347,6 +1354,9 @@
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O74" s="2"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O75" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56BAC84-8BE3-492D-AD72-B44ABA9BFED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03EE121-3916-428C-9940-7D88557D5F20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="81840" yWindow="3660" windowWidth="23235" windowHeight="12240" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="4290" yWindow="2745" windowWidth="24945" windowHeight="21255" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
   <si>
     <t>год</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>г. Варшава</t>
+  </si>
+  <si>
+    <t>Гродненская</t>
   </si>
 </sst>
 </file>
@@ -232,9 +235,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -272,7 +275,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -378,7 +381,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -520,7 +523,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -529,9 +532,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E727C47-D865-4836-8CF2-7B9647F06C78}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -543,16 +546,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:U76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.89453125" customWidth="1"/>
-    <col min="3" max="3" width="11.68359375" customWidth="1"/>
-    <col min="4" max="5" width="18.26171875" customWidth="1"/>
-    <col min="6" max="6" width="16.68359375" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
@@ -572,7 +575,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -588,7 +591,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -604,7 +607,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -618,7 +621,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -632,7 +635,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -646,7 +649,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -662,283 +665,282 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1898</v>
+      </c>
+      <c r="C8" s="8">
+        <v>66352</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="7">
         <v>1911</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B10" s="7">
         <v>1906</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
+      <c r="C10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B11" s="7">
         <v>1886</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C11" s="8">
         <v>31028</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D11" s="8">
         <v>19278</v>
       </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B12" s="7">
         <v>1889</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8">
         <v>16904</v>
       </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B13" s="7">
         <v>1909</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="8">
-        <v>23374</v>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="7">
-        <v>1889</v>
+        <v>1882</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="8">
-        <v>29004</v>
+        <v>23374</v>
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="7">
+        <v>1889</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="8">
+        <v>29004</v>
+      </c>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="7">
         <v>1898</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C16" s="2">
         <v>52166</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C16" s="2">
-        <v>47652</v>
-      </c>
-      <c r="D16" s="2">
-        <v>28698</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="7">
+        <v>1889</v>
+      </c>
+      <c r="C17" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D17" s="2">
+        <v>28698</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="7">
         <v>1899</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4" t="s">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B19" s="7">
         <v>1906</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B20" s="7">
         <v>1889</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="8">
+      <c r="C20" s="4"/>
+      <c r="D20" s="8">
         <v>18552</v>
       </c>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B21" s="7">
         <v>1898</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C21" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="8">
-        <v>16816</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C22" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="7">
+        <v>1886</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="8">
+        <v>16816</v>
+      </c>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="7">
         <v>1892</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D24" s="8">
         <v>19117</v>
       </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B25" s="7">
         <v>1882</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D25" s="8">
         <v>15122</v>
       </c>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B26" s="7">
         <v>1911</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
+      <c r="C26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B27" s="7">
         <v>1901</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C27" s="2">
         <v>103114</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="7">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>20</v>
@@ -948,190 +950,193 @@
       </c>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>13</v>
       </c>
       <c r="B29" s="7">
+        <v>1907</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="7">
         <v>1913</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E30" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="7">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E31" s="2">
-        <v>589000</v>
+        <v>575000</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="7">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E32" s="2">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="F32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="7">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E33" s="2">
-        <v>618000</v>
+        <v>603000</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>30</v>
       </c>
       <c r="B34" s="7">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E34" s="2">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="F34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="7">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E35" s="2">
-        <v>648000</v>
+        <v>633000</v>
       </c>
       <c r="F35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E36" s="2">
-        <v>664000</v>
+        <v>648000</v>
       </c>
       <c r="F36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="7">
+        <v>1887</v>
+      </c>
+      <c r="E37" s="2">
+        <v>664000</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B38" s="7">
         <v>1914</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C38" s="2">
         <v>100432</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D38" s="2">
         <v>76687</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E38" s="2">
         <v>2472605</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="2"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
       <c r="O48" s="3"/>
       <c r="P48" s="2"/>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="G49" s="2"/>
@@ -1143,7 +1148,7 @@
       <c r="O49" s="3"/>
       <c r="P49" s="2"/>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="G50" s="2"/>
@@ -1155,80 +1160,82 @@
       <c r="O50" s="3"/>
       <c r="P50" s="2"/>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
       <c r="O51" s="3"/>
       <c r="P51" s="2"/>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
       <c r="O52" s="3"/>
       <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-      <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
-    </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+    </row>
+    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-    </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-    </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-    </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="G58" s="2"/>
@@ -1238,27 +1245,27 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-    </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-    </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="G61" s="2"/>
@@ -1268,51 +1275,49 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-    </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-      <c r="O64" s="2"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
+      <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
@@ -1320,7 +1325,7 @@
       <c r="L66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -1332,31 +1337,43 @@
       <c r="L67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O71" s="2"/>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O72" s="2"/>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O73" s="2"/>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O74" s="2"/>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O75" s="2"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O76" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03EE121-3916-428C-9940-7D88557D5F20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788B6BF2-06CD-4D16-B07A-D8B9D0040011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="2745" windowWidth="24945" windowHeight="21255" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
   <si>
     <t>год</t>
   </si>
@@ -152,6 +152,24 @@
   </si>
   <si>
     <t>Гродненская</t>
+  </si>
+  <si>
+    <t>Виленская</t>
+  </si>
+  <si>
+    <t>Ковенская</t>
+  </si>
+  <si>
+    <t>Курляндская</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подольская </t>
+  </si>
+  <si>
+    <t>по ЦСК</t>
+  </si>
+  <si>
+    <t>чр и чу по ЦСК</t>
   </si>
 </sst>
 </file>
@@ -235,9 +253,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -275,7 +293,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -381,7 +399,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -523,7 +541,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -532,9 +550,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E727C47-D865-4836-8CF2-7B9647F06C78}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -546,16 +564,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U84"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.83984375" customWidth="1"/>
+    <col min="3" max="3" width="11.68359375" customWidth="1"/>
+    <col min="4" max="5" width="18.26171875" customWidth="1"/>
+    <col min="6" max="6" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
@@ -575,7 +593,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -591,7 +609,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -607,7 +625,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -621,7 +639,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -635,7 +653,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -649,7 +667,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -665,7 +683,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -679,7 +697,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -694,7 +712,7 @@
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -709,7 +727,7 @@
       </c>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -724,7 +742,7 @@
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -737,7 +755,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -752,7 +770,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -765,7 +783,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -778,7 +796,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -789,7 +807,7 @@
         <v>52166</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -803,7 +821,7 @@
         <v>28698</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -816,7 +834,7 @@
       </c>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -831,7 +849,7 @@
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -844,7 +862,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -856,7 +874,7 @@
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -869,7 +887,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -882,7 +900,7 @@
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -894,7 +912,7 @@
       </c>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -906,7 +924,7 @@
       </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -921,7 +939,7 @@
       </c>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -935,7 +953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -950,7 +968,7 @@
       </c>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -965,7 +983,7 @@
       </c>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -980,7 +998,7 @@
       </c>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -994,7 +1012,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1008,7 +1026,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -1022,7 +1040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -1036,7 +1054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -1050,7 +1068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -1064,7 +1082,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -1078,7 +1096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -1086,146 +1104,168 @@
         <v>1914</v>
       </c>
       <c r="C38" s="2">
-        <v>100432</v>
+        <v>100871</v>
       </c>
       <c r="D38" s="2">
-        <v>76687</v>
+        <v>79202</v>
       </c>
       <c r="E38" s="2">
         <v>2472605</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="F38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="7"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C40" s="2">
+        <v>60509</v>
+      </c>
+      <c r="D40" s="2">
+        <v>34087</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C41" s="2">
+        <v>62023</v>
+      </c>
+      <c r="D41" s="2">
+        <v>35541</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C42" s="2">
+        <v>51346</v>
+      </c>
+      <c r="D42" s="2">
+        <v>31414</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C43" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D43" s="2">
+        <v>11957</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C44" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D44" s="2">
+        <v>82123</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="7"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="7"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="2"/>
-    </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="2"/>
-    </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="2"/>
-    </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="2"/>
-    </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="2"/>
-    </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-    </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-    </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-      <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O56" s="3"/>
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="G57" s="2"/>
@@ -1234,38 +1274,44 @@
       <c r="J57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
-    </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O57" s="3"/>
+      <c r="P57" s="2"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
       <c r="L58" s="2"/>
-    </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="M58" s="2"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="2"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-    </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="M59" s="2"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="2"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-    </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O60" s="3"/>
+      <c r="P60" s="2"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="G61" s="2"/>
@@ -1274,47 +1320,51 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="M61" s="2"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-    </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
-      <c r="O65" s="2"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="G66" s="2"/>
@@ -1323,57 +1373,136 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
-      <c r="O66" s="2"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
+      <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
-      <c r="O67" s="2"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="O68" s="2"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="O69" s="2"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O70" s="2"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O71" s="2"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O72" s="2"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
       <c r="O73" s="2"/>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
       <c r="O74" s="2"/>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
       <c r="O75" s="2"/>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
       <c r="O76" s="2"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="O77" s="2"/>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O78" s="2"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O79" s="2"/>
+    </row>
+    <row r="80" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O81" s="2"/>
+    </row>
+    <row r="82" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O82" s="2"/>
+    </row>
+    <row r="83" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O83" s="2"/>
+    </row>
+    <row r="84" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O84" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788B6BF2-06CD-4D16-B07A-D8B9D0040011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396530AA-91EE-4656-A04C-FBDA8525763D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="76920" yWindow="2655" windowWidth="23580" windowHeight="18855" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="50">
   <si>
     <t>год</t>
   </si>
@@ -170,6 +170,18 @@
   </si>
   <si>
     <t>чр и чу по ЦСК</t>
+  </si>
+  <si>
+    <t>Дагестанская обл.</t>
+  </si>
+  <si>
+    <t>Елисаветпольская</t>
+  </si>
+  <si>
+    <t>Ферганская обл.</t>
+  </si>
+  <si>
+    <t>Уральская обл.</t>
   </si>
 </sst>
 </file>
@@ -564,7 +576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U84"/>
+  <dimension ref="A1:U88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.83984375" customWidth="1"/>
@@ -699,10 +711,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B9" s="7">
-        <v>1911</v>
+        <v>1886</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>20</v>
@@ -711,13 +723,14 @@
         <v>20</v>
       </c>
       <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B10" s="7">
-        <v>1906</v>
+        <v>1886</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>20</v>
@@ -726,73 +739,78 @@
         <v>20</v>
       </c>
       <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B11" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C11" s="8">
-        <v>31028</v>
-      </c>
-      <c r="D11" s="8">
-        <v>19278</v>
+        <v>1911</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="B12" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8">
-        <v>16904</v>
+        <v>1906</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B13" s="7">
-        <v>1909</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>20</v>
+        <v>1886</v>
+      </c>
+      <c r="C13" s="8">
+        <v>31028</v>
+      </c>
+      <c r="D13" s="8">
+        <v>19278</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B14" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C14" s="8"/>
       <c r="D14" s="8">
-        <v>23374</v>
+        <v>16904</v>
       </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="7">
-        <v>1889</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="8">
-        <v>29004</v>
+        <v>1909</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E15" s="4"/>
     </row>
@@ -801,102 +819,102 @@
         <v>7</v>
       </c>
       <c r="B16" s="7">
-        <v>1898</v>
-      </c>
-      <c r="C16" s="2">
-        <v>52166</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="8">
+        <v>23374</v>
+      </c>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="7">
         <v>1889</v>
       </c>
-      <c r="C17" s="2">
-        <v>47652</v>
-      </c>
-      <c r="D17" s="2">
-        <v>28698</v>
-      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="8">
+        <v>29004</v>
+      </c>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" s="7">
-        <v>1899</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="4"/>
+        <v>1898</v>
+      </c>
+      <c r="C18" s="2">
+        <v>52166</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" s="7">
-        <v>1906</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C19" s="2">
+        <v>47652</v>
+      </c>
+      <c r="D19" s="2">
+        <v>28698</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B20" s="7">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="8">
-        <v>18552</v>
+      <c r="D20" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="7">
-        <v>1898</v>
+        <v>1906</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" s="7">
-        <v>1882</v>
-      </c>
-      <c r="C22" s="2">
-        <v>22197</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>1889</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="8">
+        <v>18552</v>
+      </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B23" s="7">
-        <v>1886</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="8">
-        <v>16816</v>
+        <v>1898</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="E23" s="4"/>
     </row>
@@ -905,60 +923,57 @@
         <v>36</v>
       </c>
       <c r="B24" s="7">
-        <v>1892</v>
-      </c>
-      <c r="D24" s="8">
-        <v>19117</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="C24" s="2">
+        <v>22197</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" s="7">
-        <v>1882</v>
-      </c>
+        <v>1886</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" s="8">
-        <v>15122</v>
+        <v>16816</v>
       </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B26" s="7">
-        <v>1911</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>20</v>
+        <v>1892</v>
+      </c>
+      <c r="D26" s="8">
+        <v>19117</v>
       </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7">
-        <v>1901</v>
-      </c>
-      <c r="C27" s="2">
-        <v>103114</v>
-      </c>
-      <c r="F27" t="s">
-        <v>25</v>
-      </c>
+        <v>1882</v>
+      </c>
+      <c r="D27" s="8">
+        <v>15122</v>
+      </c>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28" s="7">
-        <v>1904</v>
+        <v>1911</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>20</v>
@@ -970,10 +985,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B29" s="7">
-        <v>1907</v>
+        <v>1895</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>20</v>
@@ -985,10 +1000,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B30" s="7">
-        <v>1913</v>
+        <v>1889</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>20</v>
@@ -1000,69 +1015,72 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B31" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E31" s="2">
-        <v>575000</v>
+        <v>1901</v>
+      </c>
+      <c r="C31" s="2">
+        <v>103114</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B32" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E32" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F32" t="s">
-        <v>31</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B33" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E33" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F33" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B34" s="7">
-        <v>1884</v>
-      </c>
-      <c r="E34" s="2">
-        <v>618000</v>
-      </c>
-      <c r="F34" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="7">
-        <v>1885</v>
+        <v>1881</v>
       </c>
       <c r="E35" s="2">
-        <v>633000</v>
+        <v>575000</v>
       </c>
       <c r="F35" t="s">
         <v>31</v>
@@ -1073,10 +1091,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="7">
-        <v>1886</v>
+        <v>1882</v>
       </c>
       <c r="E36" s="2">
-        <v>648000</v>
+        <v>589000</v>
       </c>
       <c r="F36" t="s">
         <v>31</v>
@@ -1087,10 +1105,10 @@
         <v>30</v>
       </c>
       <c r="B37" s="7">
-        <v>1887</v>
+        <v>1883</v>
       </c>
       <c r="E37" s="2">
-        <v>664000</v>
+        <v>603000</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -1098,114 +1116,98 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B38" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C38" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D38" s="2">
-        <v>79202</v>
+        <v>1884</v>
       </c>
       <c r="E38" s="2">
-        <v>2472605</v>
+        <v>618000</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="7"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="7">
+        <v>1885</v>
+      </c>
+      <c r="E39" s="2">
+        <v>633000</v>
+      </c>
+      <c r="F39" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B40" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C40" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D40" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E40" s="2"/>
+        <v>1886</v>
+      </c>
+      <c r="E40" s="2">
+        <v>648000</v>
+      </c>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C41" s="2">
-        <v>62023</v>
-      </c>
-      <c r="D41" s="2">
-        <v>35541</v>
-      </c>
-      <c r="E41" s="2"/>
+        <v>1887</v>
+      </c>
+      <c r="E41" s="2">
+        <v>664000</v>
+      </c>
       <c r="F41" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B42" s="7">
         <v>1914</v>
       </c>
       <c r="C42" s="2">
-        <v>51346</v>
+        <v>100871</v>
       </c>
       <c r="D42" s="2">
-        <v>31414</v>
-      </c>
-      <c r="E42" s="2"/>
+        <v>79202</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2472605</v>
+      </c>
       <c r="F42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C43" s="2">
-        <v>14341</v>
-      </c>
-      <c r="D43" s="2">
-        <v>11957</v>
-      </c>
+      <c r="B43" s="7"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B44" s="7">
         <v>1914</v>
       </c>
       <c r="C44" s="2">
-        <v>142692</v>
+        <v>60509</v>
       </c>
       <c r="D44" s="2">
-        <v>82123</v>
+        <v>34087</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
@@ -1213,168 +1215,201 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="7"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C45" s="2">
+        <v>62023</v>
+      </c>
+      <c r="D45" s="2">
+        <v>35541</v>
+      </c>
       <c r="E45" s="2"/>
+      <c r="F45" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="7"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C46" s="2">
+        <v>51346</v>
+      </c>
+      <c r="D46" s="2">
+        <v>31414</v>
+      </c>
       <c r="E46" s="2"/>
+      <c r="F46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C47" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D47" s="2">
+        <v>11957</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C48" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D48" s="2">
+        <v>82123</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="7"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="7"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" t="s">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="2"/>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="2"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="2"/>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="2"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-      <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
       <c r="O60" s="3"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="O61" s="3"/>
       <c r="P61" s="2"/>
-      <c r="Q61" s="2"/>
-      <c r="T61" s="2"/>
-      <c r="U61" s="2"/>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="2"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="O63" s="3"/>
+      <c r="P63" s="2"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O64" s="3"/>
+      <c r="P64" s="2"/>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O65" s="3"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="G67" s="2"/>
@@ -1383,28 +1418,27 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M67" s="2"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
       <c r="L69" s="2"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="M69" s="2"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="G70" s="2"/>
@@ -1414,36 +1448,37 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
-      <c r="O73" s="2"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="G74" s="2"/>
@@ -1452,57 +1487,96 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
-      <c r="O74" s="2"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
+      <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="O75" s="2"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
+      <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
-      <c r="O76" s="2"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
       <c r="O77" s="2"/>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
       <c r="O78" s="2"/>
     </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
       <c r="O79" s="2"/>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
       <c r="O80" s="2"/>
     </row>
-    <row r="81" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
       <c r="O81" s="2"/>
     </row>
-    <row r="82" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="11:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O82" s="2"/>
     </row>
-    <row r="83" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="11:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O83" s="2"/>
     </row>
-    <row r="84" spans="15:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="11:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O84" s="2"/>
+    </row>
+    <row r="85" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O85" s="2"/>
+    </row>
+    <row r="86" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O86" s="2"/>
+    </row>
+    <row r="87" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O87" s="2"/>
+    </row>
+    <row r="88" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O88" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396530AA-91EE-4656-A04C-FBDA8525763D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A02FE3C-186B-4727-82B0-1DE6FDCB4529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76920" yWindow="2655" windowWidth="23580" windowHeight="18855" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="51">
   <si>
     <t>год</t>
   </si>
@@ -172,16 +172,19 @@
     <t>чр и чу по ЦСК</t>
   </si>
   <si>
+    <t>Ферганская обл.</t>
+  </si>
+  <si>
+    <t>Уральская обл.</t>
+  </si>
+  <si>
     <t>Дагестанская обл.</t>
   </si>
   <si>
     <t>Елисаветпольская</t>
   </si>
   <si>
-    <t>Ферганская обл.</t>
-  </si>
-  <si>
-    <t>Уральская обл.</t>
+    <t>A 1887 1888</t>
   </si>
 </sst>
 </file>
@@ -711,32 +714,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" s="7">
         <v>1886</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="7">
         <v>1886</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
@@ -985,7 +988,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="7">
         <v>1895</v>
@@ -1000,7 +1003,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B30" s="7">
         <v>1889</v>

--- a/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A02FE3C-186B-4727-82B0-1DE6FDCB4529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79EB69C-1AE0-49DA-8C75-DB546431B4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="72540" yWindow="825" windowWidth="27915" windowHeight="18855" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
   <si>
     <t>год</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>A 1887 1888</t>
+  </si>
+  <si>
+    <t>Черниговская</t>
   </si>
 </sst>
 </file>
@@ -579,7 +582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U88"/>
+  <dimension ref="A1:U91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.83984375" customWidth="1"/>
@@ -1032,100 +1035,95 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B32" s="7">
-        <v>1904</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="4"/>
+        <v>1881</v>
+      </c>
+      <c r="C32" s="2">
+        <v>88569</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="7">
-        <v>1907</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="4"/>
+        <v>1881</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2">
+        <v>5330</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="7">
-        <v>1913</v>
+        <v>1882</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="4"/>
+      <c r="D34" s="2">
+        <v>5235</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B35" s="7">
-        <v>1881</v>
-      </c>
-      <c r="E35" s="2">
-        <v>575000</v>
-      </c>
-      <c r="F35" t="s">
-        <v>31</v>
-      </c>
+        <v>1904</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="4"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B36" s="7">
-        <v>1882</v>
-      </c>
-      <c r="E36" s="2">
-        <v>589000</v>
-      </c>
-      <c r="F36" t="s">
-        <v>31</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B37" s="7">
-        <v>1883</v>
-      </c>
-      <c r="E37" s="2">
-        <v>603000</v>
-      </c>
-      <c r="F37" t="s">
-        <v>31</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>30</v>
       </c>
       <c r="B38" s="7">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="E38" s="2">
-        <v>618000</v>
+        <v>575000</v>
       </c>
       <c r="F38" t="s">
         <v>31</v>
@@ -1136,10 +1134,10 @@
         <v>30</v>
       </c>
       <c r="B39" s="7">
-        <v>1885</v>
+        <v>1882</v>
       </c>
       <c r="E39" s="2">
-        <v>633000</v>
+        <v>589000</v>
       </c>
       <c r="F39" t="s">
         <v>31</v>
@@ -1150,10 +1148,10 @@
         <v>30</v>
       </c>
       <c r="B40" s="7">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="E40" s="2">
-        <v>648000</v>
+        <v>603000</v>
       </c>
       <c r="F40" t="s">
         <v>31</v>
@@ -1164,10 +1162,10 @@
         <v>30</v>
       </c>
       <c r="B41" s="7">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="E41" s="2">
-        <v>664000</v>
+        <v>618000</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -1175,96 +1173,84 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B42" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C42" s="2">
-        <v>100871</v>
-      </c>
-      <c r="D42" s="2">
-        <v>79202</v>
+        <v>1885</v>
       </c>
       <c r="E42" s="2">
-        <v>2472605</v>
+        <v>633000</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="7"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="7">
+        <v>1886</v>
+      </c>
+      <c r="E43" s="2">
+        <v>648000</v>
+      </c>
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B44" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C44" s="2">
-        <v>60509</v>
-      </c>
-      <c r="D44" s="2">
-        <v>34087</v>
-      </c>
-      <c r="E44" s="2"/>
+        <v>1887</v>
+      </c>
+      <c r="E44" s="2">
+        <v>664000</v>
+      </c>
       <c r="F44" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B45" s="7">
         <v>1914</v>
       </c>
       <c r="C45" s="2">
-        <v>62023</v>
+        <v>100871</v>
       </c>
       <c r="D45" s="2">
-        <v>35541</v>
-      </c>
-      <c r="E45" s="2"/>
+        <v>79202</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2472605</v>
+      </c>
       <c r="F45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="7">
-        <v>1914</v>
-      </c>
-      <c r="C46" s="2">
-        <v>51346</v>
-      </c>
-      <c r="D46" s="2">
-        <v>31414</v>
-      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B47" s="7">
         <v>1914</v>
       </c>
       <c r="C47" s="2">
-        <v>14341</v>
+        <v>60509</v>
       </c>
       <c r="D47" s="2">
-        <v>11957</v>
+        <v>34087</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s">
@@ -1273,16 +1259,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B48" s="7">
         <v>1914</v>
       </c>
       <c r="C48" s="2">
-        <v>142692</v>
+        <v>62023</v>
       </c>
       <c r="D48" s="2">
-        <v>82123</v>
+        <v>35541</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s">
@@ -1290,91 +1276,109 @@
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="7"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="A49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C49" s="2">
+        <v>51346</v>
+      </c>
+      <c r="D49" s="2">
+        <v>31414</v>
+      </c>
       <c r="E49" s="2"/>
+      <c r="F49" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="7"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="A50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C50" s="2">
+        <v>14341</v>
+      </c>
+      <c r="D50" s="2">
+        <v>11957</v>
+      </c>
       <c r="E50" s="2"/>
+      <c r="F50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="7">
+        <v>1914</v>
+      </c>
+      <c r="C51" s="2">
+        <v>142692</v>
+      </c>
+      <c r="D51" s="2">
+        <v>82123</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="1" t="s">
+      <c r="B52" s="7"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="7"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="2"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="2"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="2"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
       <c r="O63" s="3"/>
       <c r="P63" s="2"/>
     </row>
@@ -1385,6 +1389,8 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
       <c r="O64" s="3"/>
       <c r="P64" s="2"/>
     </row>
@@ -1395,14 +1401,10 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="O65" s="3"/>
       <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-      <c r="T65" s="2"/>
-      <c r="U65" s="2"/>
     </row>
     <row r="66" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="2"/>
@@ -1411,6 +1413,10 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="2"/>
     </row>
     <row r="67" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="2"/>
@@ -1419,9 +1425,8 @@
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="2"/>
     </row>
     <row r="68" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="2"/>
@@ -1430,6 +1435,14 @@
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
     </row>
     <row r="69" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="2"/>
@@ -1438,8 +1451,6 @@
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
     </row>
     <row r="70" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="2"/>
@@ -1450,6 +1461,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="2"/>
@@ -1458,8 +1470,6 @@
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
     </row>
     <row r="72" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="2"/>
@@ -1468,8 +1478,8 @@
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
     </row>
     <row r="73" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="2"/>
@@ -1518,7 +1528,8 @@
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
     </row>
     <row r="78" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="2"/>
@@ -1527,59 +1538,88 @@
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
     </row>
     <row r="79" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
+      <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
-      <c r="O79" s="2"/>
     </row>
     <row r="80" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
+      <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
       <c r="O80" s="2"/>
     </row>
-    <row r="81" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
       <c r="O81" s="2"/>
     </row>
-    <row r="82" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
       <c r="O82" s="2"/>
     </row>
-    <row r="83" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
       <c r="O83" s="2"/>
     </row>
-    <row r="84" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
       <c r="O84" s="2"/>
     </row>
-    <row r="85" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O85" s="2"/>
     </row>
-    <row r="86" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O86" s="2"/>
     </row>
-    <row r="87" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O87" s="2"/>
     </row>
-    <row r="88" spans="11:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O88" s="2"/>
+    </row>
+    <row r="89" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O89" s="2"/>
+    </row>
+    <row r="90" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O90" s="2"/>
+    </row>
+    <row r="91" spans="2:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="O91" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
